--- a/DownloadedExcels/OutletExcel.xlsx
+++ b/DownloadedExcels/OutletExcel.xlsx
@@ -65,7 +65,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AF17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" style="1" width="8.0" customWidth="false"/>
@@ -259,12 +259,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>1000000014</t>
+          <t>1000000013</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Aautomation_Outlet_14</t>
+          <t>Aautomation_Outlet_13</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -304,7 +304,7 @@
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>CA505</t>
+          <t>CA506</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
@@ -314,7 +314,7 @@
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>CA308</t>
+          <t>CA307</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
@@ -329,19 +329,19 @@
       </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
+          <t>CA902</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>CA1201</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
       <c r="S2" s="1" t="inlineStr">
         <is>
           <t>CA404</t>
@@ -349,12 +349,12 @@
       </c>
       <c r="T2" s="1" t="inlineStr">
         <is>
-          <t>CA70</t>
+          <t>ICA603</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>12345678915</t>
+          <t/>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -421,12 +421,12 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>C0000050002</t>
+          <t>1000000015</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>SANITY SHORT OUTLE</t>
+          <t>Automation_Outlet_15</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -436,12 +436,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>44.45631000000000000000</t>
+          <t>25.7291</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>44.45631000000000000000</t>
+          <t>05.8844</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -456,116 +456,122 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>CA506</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>CP2T1</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>CA308</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>CA1102</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>CA909</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>CA409</t>
+        </is>
+      </c>
+      <c r="T3" s="1" t="inlineStr">
+        <is>
+          <t>CA70</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y3" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>Y</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>CA506</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>CA2T2</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>CA303</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>CA1002</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>CA1105</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
-        <is>
-          <t>CA901</t>
-        </is>
-      </c>
-      <c r="Q3" s="1" t="inlineStr">
-        <is>
-          <t>CA1299</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="inlineStr">
-        <is>
-          <t>CA801</t>
-        </is>
-      </c>
-      <c r="S3" s="1" t="inlineStr">
-        <is>
-          <t>CA405</t>
-        </is>
-      </c>
-      <c r="T3" s="1" t="inlineStr">
-        <is>
-          <t>CA701</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>03076308094</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y3" s="1" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>300000.0</v>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
     </row>
@@ -577,12 +583,12 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>C0124183239</t>
+          <t>1000000016</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Shah baba</t>
+          <t>Automation_Outlet_16</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -592,12 +598,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>67.14471451</t>
+          <t>25.7291</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>24.82096462</t>
+          <t>05.8844</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -607,7 +613,7 @@
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -622,12 +628,12 @@
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>CA503</t>
+          <t>CA506</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr">
         <is>
-          <t>CA2T5</t>
+          <t>CP2T1</t>
         </is>
       </c>
       <c r="M4" s="1" t="inlineStr">
@@ -637,42 +643,42 @@
       </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>ICNI2020</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>CA1106</t>
+          <t>CA1102</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
         <is>
-          <t>CA905</t>
+          <t>CA998</t>
         </is>
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>CA1209</t>
+          <t>CA1201</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr">
         <is>
-          <t>IC10OIA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>CA405</t>
+          <t>CA404</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr">
         <is>
-          <t>CA703</t>
+          <t>CA70</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>03076308095</t>
+          <t/>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -692,36 +698,42 @@
       </c>
       <c r="Y4" s="1" t="inlineStr">
         <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>250000.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t/>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t/>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="n">
-        <v>10.0</v>
+          <t/>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -733,12 +745,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>C0124183241</t>
+          <t>1000000018</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>TT Traders</t>
+          <t>Automation_Outlet_18</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -748,12 +760,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>67.14051833</t>
+          <t>25.7291</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24.825125</t>
+          <t>05.8844</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -763,7 +775,7 @@
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>0002</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -778,106 +790,2056 @@
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>CA502</t>
+          <t>CA506</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr">
         <is>
-          <t>CA2T5</t>
+          <t>CA2T2</t>
         </is>
       </c>
       <c r="M5" s="1" t="inlineStr">
         <is>
+          <t>CA307</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>CA1002</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>CA1103</t>
+        </is>
+      </c>
+      <c r="P5" s="1" t="inlineStr">
+        <is>
+          <t>CA902</t>
+        </is>
+      </c>
+      <c r="Q5" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R5" s="1" t="inlineStr">
+        <is>
+          <t>CA801</t>
+        </is>
+      </c>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>CA404</t>
+        </is>
+      </c>
+      <c r="T5" s="1" t="inlineStr">
+        <is>
+          <t>CA701</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y5" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>50250327</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>1000000019</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Automation_Outlet_19</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>C11672</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25.7291</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>05.8844</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>CA505</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>CP2T1</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
           <t>CA308</t>
         </is>
       </c>
-      <c r="N5" s="1" t="inlineStr">
-        <is>
-          <t>ICCP2020</t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="inlineStr">
-        <is>
-          <t>CA1105</t>
-        </is>
-      </c>
-      <c r="P5" s="1" t="inlineStr">
-        <is>
-          <t>CA910</t>
-        </is>
-      </c>
-      <c r="Q5" s="1" t="inlineStr">
-        <is>
-          <t>CA1202</t>
-        </is>
-      </c>
-      <c r="R5" s="1" t="inlineStr">
-        <is>
-          <t>IC11OIA</t>
-        </is>
-      </c>
-      <c r="S5" s="1" t="inlineStr">
-        <is>
-          <t>CA403</t>
-        </is>
-      </c>
-      <c r="T5" s="1" t="inlineStr">
-        <is>
-          <t>CA706</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>03076308096</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Y5" s="1" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="AA5" s="2" t="n">
-        <v>250000.0</v>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>IC21SA</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>CA998</t>
+        </is>
+      </c>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R6" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>CA404</t>
+        </is>
+      </c>
+      <c r="T6" s="1" t="inlineStr">
+        <is>
+          <t>CA70</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y6" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>50250327</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>1000000020</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Automation_Outlet_20</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>C11672</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>25.7291</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>05.8844</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>CA505</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>CA2T3</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="inlineStr">
+        <is>
+          <t>CA308</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>CA1101</t>
+        </is>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>CA909</t>
+        </is>
+      </c>
+      <c r="Q7" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R7" s="1" t="inlineStr">
+        <is>
+          <t>CA801</t>
+        </is>
+      </c>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>CA404</t>
+        </is>
+      </c>
+      <c r="T7" s="1" t="inlineStr">
+        <is>
+          <t>CA701</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y7" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>50250327</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>1000000031</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Automation_Outlet_31</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>C11672</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>25.7291</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>05.8844</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R8" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T8" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y8" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>50250327</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>1000000032</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Automation_Outlet_32</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>C11672</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>25.7291</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>05.8844</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="AE5" s="2" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="AF5" t="inlineStr">
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M9" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R9" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S9" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T9" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y9" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>50250327</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>1000000033</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Automation_Outlet_33</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>C11672</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>25.7291</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>05.8844</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R10" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S10" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T10" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y10" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>50250327</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>1000000034</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Automation_Outlet_34</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>C11672</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>25.7291</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>05.8844</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R11" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S11" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T11" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y11" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>50250327</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>1000000035</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Automation_Outlet_35</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>C11672</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>25.7291</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>05.8844</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y12" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>50250327</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>1000000036</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Automation_Outlet_36</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>C11672</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>25.7291</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>05.8844</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y13" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>50250327</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>1000000037</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Automation_Outlet_37</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>C11672</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>25.7291</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>05.8844</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y14" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>50250327</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>1000000038</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Automation_Outlet_38</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>C11672</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>25.7291</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>05.8844</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q15" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y15" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>50250327</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>1000000039</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Automation_Outlet_39</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>C11672</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>25.7291</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>05.8844</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q16" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y16" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>50250327</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>1000000040</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Automation_Outlet_40</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>C11672</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>25.7291</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>05.8844</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q17" s="1" t="inlineStr">
+        <is>
+          <t>CA1201</t>
+        </is>
+      </c>
+      <c r="R17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Y17" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>

--- a/DownloadedExcels/OutletExcel.xlsx
+++ b/DownloadedExcels/OutletExcel.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>R</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t/>
+          <t>55555-1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
